--- a/Dashboards/data/Data final/ingresos/inglab_area.xlsx
+++ b/Dashboards/data/Data final/ingresos/inglab_area.xlsx
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>495.75</v>
+        <v>492.22</v>
       </c>
     </row>
     <row r="37">
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>301.84</v>
+        <v>308.15</v>
       </c>
     </row>
     <row r="38">
@@ -923,7 +923,7 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>524.41</v>
+        <v>533.33</v>
       </c>
     </row>
     <row r="39">
@@ -936,7 +936,7 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>311.81</v>
+        <v>325.59</v>
       </c>
     </row>
     <row r="40">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="C40" t="n">
-        <v>514.34</v>
+        <v>511.57</v>
       </c>
     </row>
     <row r="41">
@@ -962,7 +962,7 @@
         </is>
       </c>
       <c r="C41" t="n">
-        <v>334.69</v>
+        <v>338.37</v>
       </c>
     </row>
     <row r="42">
@@ -975,7 +975,7 @@
         </is>
       </c>
       <c r="C42" t="n">
-        <v>522.26</v>
+        <v>492.36</v>
       </c>
     </row>
     <row r="43">
@@ -988,7 +988,7 @@
         </is>
       </c>
       <c r="C43" t="n">
-        <v>324.22</v>
+        <v>336.48</v>
       </c>
     </row>
     <row r="44">
@@ -1001,7 +1001,7 @@
         </is>
       </c>
       <c r="C44" t="n">
-        <v>541.2</v>
+        <v>566.53</v>
       </c>
     </row>
     <row r="45">
@@ -1014,7 +1014,7 @@
         </is>
       </c>
       <c r="C45" t="n">
-        <v>343.56</v>
+        <v>388.54</v>
       </c>
     </row>
     <row r="46">
@@ -1248,7 +1248,7 @@
         </is>
       </c>
       <c r="C63" t="n">
-        <v>439.25</v>
+        <v>438.23</v>
       </c>
     </row>
     <row r="64">
@@ -1261,7 +1261,7 @@
         </is>
       </c>
       <c r="C64" t="n">
-        <v>462.76</v>
+        <v>471.35</v>
       </c>
     </row>
     <row r="65">
@@ -1274,7 +1274,7 @@
         </is>
       </c>
       <c r="C65" t="n">
-        <v>462.36</v>
+        <v>460.61</v>
       </c>
     </row>
     <row r="66">
@@ -1287,7 +1287,7 @@
         </is>
       </c>
       <c r="C66" t="n">
-        <v>463.82</v>
+        <v>447.25</v>
       </c>
     </row>
     <row r="67">
@@ -1300,7 +1300,7 @@
         </is>
       </c>
       <c r="C67" t="n">
-        <v>483</v>
+        <v>514.4299999999999</v>
       </c>
     </row>
   </sheetData>
